--- a/тест-съют на заказ карты.xlsx
+++ b/тест-съют на заказ карты.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TestProjectIntern_n1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B014EDED-7FFE-4EF8-BFD9-F0B099E90DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8143FD1-0276-4EB4-9B00-3A4162D8F67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{FB7EE499-4B03-4CD7-9099-B4F6E01EF725}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB7EE499-4B03-4CD7-9099-B4F6E01EF725}"/>
   </bookViews>
   <sheets>
     <sheet name="Тест-кейс №1" sheetId="2" r:id="rId1"/>
@@ -589,173 +589,173 @@
   <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1087,198 +1087,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="48">
+      <c r="B1" s="26">
         <v>1</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="50"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="39" t="s">
+      <c r="B4" s="34"/>
+      <c r="C4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="36" t="s">
+      <c r="B5" s="36"/>
+      <c r="C5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="29"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="42"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="25"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="45"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="25"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="45"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="21" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="20"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="14" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="20"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="14" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="14" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" ht="409.5" customHeight="1">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="25"/>
+      <c r="D15" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="246.75" customHeight="1">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="25"/>
+      <c r="D16" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="183" customHeight="1">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="5" t="s">
+      <c r="C17" s="25"/>
+      <c r="D17" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="36" customHeight="1">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="10"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="6"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="51"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="2"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
@@ -1288,6 +1288,10 @@
     <row r="69" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:C13"/>
     <mergeCell ref="B15:C15"/>
@@ -1300,10 +1304,6 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{1293ADC1-AF1B-4242-BC4D-79642795DC93}"/>
@@ -1330,186 +1330,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="50"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="39" t="s">
+      <c r="B4" s="34"/>
+      <c r="C4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="36" t="s">
+      <c r="B5" s="36"/>
+      <c r="C5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="29"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="42"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="25"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="45"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="25"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="45"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="21" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="20"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="14" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="20"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="14" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="14" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" ht="243.75" customHeight="1">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="25"/>
+      <c r="D15" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="10"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" ht="24" customHeight="1">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="6"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="51"/>
     </row>
     <row r="18" spans="1:4" ht="30.75" customHeight="1">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="2"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="48"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="56"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="56"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="14"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A20" s="56"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="56"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="14"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
@@ -1519,6 +1519,10 @@
     <row r="69" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:C13"/>
     <mergeCell ref="B15:C15"/>
@@ -1531,10 +1535,6 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B17:D17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{115A8FA8-A0AA-49D0-8EC3-0A6A077B36FD}"/>
@@ -1561,186 +1561,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="50"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="39" t="s">
+      <c r="B4" s="34"/>
+      <c r="C4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="36" t="s">
+      <c r="B5" s="36"/>
+      <c r="C5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="29"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="42"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="25"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="45"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="25"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="45"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="21" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="20"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="14" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="20"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="14" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="14" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" ht="186" customHeight="1">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="54"/>
+      <c r="D15" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="10"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="6"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="51"/>
     </row>
     <row r="18" spans="1:4" ht="30.75" customHeight="1">
-      <c r="A18" s="55" t="s">
+      <c r="A18" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="52"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="57"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="57"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="57"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="15"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A20" s="56"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="56"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="14"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
@@ -1750,6 +1750,10 @@
     <row r="69" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:C13"/>
     <mergeCell ref="B15:C15"/>
@@ -1762,10 +1766,6 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B17:D17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{4C9C0884-9E06-4163-ACD6-7417932F33A8}"/>
@@ -1792,198 +1792,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="48">
+      <c r="B1" s="26">
         <v>4</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="50"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="39" t="s">
+      <c r="B4" s="34"/>
+      <c r="C4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="36" t="s">
+      <c r="B5" s="36"/>
+      <c r="C5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="29"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="42"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="25"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="45"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="25"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="45"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="21" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="A11" s="20"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="14" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="20"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="14" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="14" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" ht="409.5" customHeight="1">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="25"/>
+      <c r="D15" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="408.75" customHeight="1">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="25"/>
+      <c r="D16" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="111.75" customHeight="1">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="5" t="s">
+      <c r="C17" s="25"/>
+      <c r="D17" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="33.75" customHeight="1">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="10"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4" ht="23.25" customHeight="1">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="6"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="51"/>
     </row>
     <row r="20" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="2"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1"/>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
@@ -1993,6 +1993,10 @@
     <row r="69" s="1" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:C13"/>
     <mergeCell ref="B15:C15"/>
@@ -2005,10 +2009,6 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{55C645FF-83E9-49DE-AED9-044391D15655}"/>
